--- a/product_selector_out/STM32H7B0 value line.xlsx
+++ b/product_selector_out/STM32H7B0 value line.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3309,9 +3309,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -3324,12 +3324,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3349,7 +3349,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3359,7 +3359,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3369,19 +3369,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -3389,27 +3389,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3419,12 +3419,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AA12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB12" s="8" t="inlineStr">
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3444,12 +3444,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3459,32 +3459,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3514,29 +3514,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -3559,52 +3559,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3619,9 +3619,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3646,9 +3646,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3661,12 +3661,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3686,7 +3686,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3696,7 +3696,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3706,19 +3706,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -3726,27 +3726,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3756,12 +3756,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AA13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB13" s="8" t="inlineStr">
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3781,12 +3781,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3796,32 +3796,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3851,29 +3851,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -3896,52 +3896,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3956,9 +3956,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3983,9 +3983,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3998,12 +3998,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4023,7 +4023,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4033,7 +4033,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4043,19 +4043,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -4063,27 +4063,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4093,12 +4093,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AA14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB14" s="8" t="inlineStr">
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4113,17 +4113,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4133,32 +4133,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4188,12 +4188,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="8" t="inlineStr">
+      <c r="AT14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4203,14 +4203,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -4233,52 +4233,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4293,9 +4293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -4335,12 +4335,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4360,7 +4360,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4370,7 +4370,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4380,7 +4380,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4400,27 +4400,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4430,12 +4430,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="8" t="inlineStr">
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4450,17 +4450,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4470,32 +4470,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4525,17 +4525,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
+      <c r="AT15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4545,7 +4545,7 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
+      <c r="AX15" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -4570,52 +4570,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4657,9 +4657,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -4672,12 +4672,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4697,7 +4697,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4707,7 +4707,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4717,19 +4717,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -4737,27 +4737,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4772,7 +4772,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB16" s="8" t="inlineStr">
+      <c r="AB16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4792,12 +4792,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4807,32 +4807,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4862,29 +4862,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -4907,52 +4907,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4967,9 +4967,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32H7B0ZB</t>
+          <t>STM32H7B0AB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5044,7 +5044,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32H7B0ZB</t>
+          <t>STM32H7B0AB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32H7B0ZB</t>
+          <t>STM32H7B0AB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5081,271 +5081,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32H7B0VB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32H7B0VB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32H7B0VB</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32H7B0IB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32H7B0IB</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32H7B0IB</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32H7B0AB</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32H7B0AB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32H7B0AB</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32H7B0RB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32H7B0RB</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32H7B0RB</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H7B0 value line.xlsx
+++ b/product_selector_out/STM32H7B0 value line.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -3309,9 +3309,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -3324,12 +3324,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3349,7 +3349,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3359,7 +3359,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3369,19 +3369,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -3389,27 +3389,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3419,12 +3419,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AA12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB12" s="7" t="inlineStr">
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3444,12 +3444,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="7" t="inlineStr">
+      <c r="AF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3459,32 +3459,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3514,29 +3514,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -3559,52 +3559,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3619,9 +3619,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3646,9 +3646,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3661,12 +3661,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3686,7 +3686,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3696,7 +3696,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3706,19 +3706,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -3726,27 +3726,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3756,12 +3756,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AA13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB13" s="7" t="inlineStr">
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3781,12 +3781,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="7" t="inlineStr">
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3796,32 +3796,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3851,29 +3851,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -3896,52 +3896,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3956,9 +3956,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3983,9 +3983,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3998,12 +3998,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4023,7 +4023,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4033,7 +4033,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4043,19 +4043,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -4063,27 +4063,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4093,12 +4093,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AA14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB14" s="7" t="inlineStr">
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4113,17 +4113,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4133,32 +4133,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4188,12 +4188,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="7" t="inlineStr">
+      <c r="AT14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4203,14 +4203,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -4233,52 +4233,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4293,9 +4293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -4335,12 +4335,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4360,7 +4360,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4370,7 +4370,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4380,7 +4380,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4400,27 +4400,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4430,12 +4430,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AA15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="7" t="inlineStr">
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4450,17 +4450,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4470,32 +4470,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4525,17 +4525,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="7" t="inlineStr">
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4545,7 +4545,7 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="8" t="inlineStr">
+      <c r="AX15" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -4570,52 +4570,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4657,9 +4657,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -4672,12 +4672,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4697,7 +4697,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4707,7 +4707,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4717,19 +4717,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -4737,27 +4737,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4772,7 +4772,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB16" s="7" t="inlineStr">
+      <c r="AB16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4792,12 +4792,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="7" t="inlineStr">
+      <c r="AF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4807,32 +4807,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4862,29 +4862,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -4907,52 +4907,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4967,9 +4967,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32H7B0AB</t>
+          <t>STM32H7B0ZB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5044,7 +5044,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32H7B0AB</t>
+          <t>STM32H7B0ZB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5066,20 +5066,284 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>STM32H7B0ZB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32H7B0VB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32H7B0VB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32H7B0VB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32H7B0IB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32H7B0IB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32H7B0IB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>STM32H7B0AB</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32H7B0AB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32H7B0AB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32H7B0RB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32H7B0RB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32H7B0RB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32H7B0 value line.xlsx
+++ b/product_selector_out/STM32H7B0 value line.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO16"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.74609375" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -2686,12 +2713,17 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2714,12 +2746,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -2734,9 +2768,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -2777,7 +2810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO16"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2847,6 +2880,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3190,6 +3224,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -3287,6 +3326,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3619,7 +3659,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3956,7 +4001,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4293,7 +4343,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4630,7 +4685,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4967,7 +5027,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4975,8 +5040,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
